--- a/artfynd/A 42062-2024 artfynd.xlsx
+++ b/artfynd/A 42062-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120482874</v>
+        <v>120482728</v>
       </c>
       <c r="B3" t="n">
-        <v>80177</v>
+        <v>74466</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,21 +822,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466131</v>
+        <v>465970</v>
       </c>
       <c r="R3" t="n">
-        <v>6230670</v>
+        <v>6230550</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120483084</v>
+        <v>120482874</v>
       </c>
       <c r="B4" t="n">
-        <v>91801</v>
+        <v>80177</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,21 +948,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>230185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465969</v>
+        <v>466131</v>
       </c>
       <c r="R4" t="n">
-        <v>6230789</v>
+        <v>6230670</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1030,17 +1030,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120482728</v>
+        <v>120483084</v>
       </c>
       <c r="B5" t="n">
-        <v>74466</v>
+        <v>91801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465970</v>
+        <v>465969</v>
       </c>
       <c r="R5" t="n">
-        <v>6230550</v>
+        <v>6230789</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1310,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120483089</v>
+        <v>120483051</v>
       </c>
       <c r="B7" t="n">
-        <v>74466</v>
+        <v>94344</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1326,26 +1326,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1353,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465969</v>
+        <v>466118</v>
       </c>
       <c r="R7" t="n">
-        <v>6230789</v>
+        <v>6230904</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1404,21 +1405,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120483051</v>
+        <v>120482958</v>
       </c>
       <c r="B8" t="n">
-        <v>94344</v>
+        <v>80177</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,27 +1438,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>230185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1480,10 +1465,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466118</v>
+        <v>466104</v>
       </c>
       <c r="R8" t="n">
-        <v>6230904</v>
+        <v>6230737</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1531,6 +1516,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120483065</v>
+        <v>120482856</v>
       </c>
       <c r="B9" t="n">
         <v>80177</v>
@@ -1587,14 +1587,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Torparevången, Sk</t>
+          <t>N Blistorp, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465978</v>
+        <v>466127</v>
       </c>
       <c r="R9" t="n">
-        <v>6230874</v>
+        <v>6230654</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1646,17 +1646,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482958</v>
+        <v>120483065</v>
       </c>
       <c r="B10" t="n">
         <v>80177</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466104</v>
+        <v>465978</v>
       </c>
       <c r="R10" t="n">
-        <v>6230737</v>
+        <v>6230874</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120482961</v>
+        <v>120483089</v>
       </c>
       <c r="B11" t="n">
-        <v>80177</v>
+        <v>74466</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466096</v>
+        <v>465969</v>
       </c>
       <c r="R11" t="n">
-        <v>6230831</v>
+        <v>6230789</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120482856</v>
+        <v>120482961</v>
       </c>
       <c r="B12" t="n">
         <v>80177</v>
@@ -1965,14 +1965,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Blistorp, Sk</t>
+          <t>N Torparevången, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466127</v>
+        <v>466096</v>
       </c>
       <c r="R12" t="n">
-        <v>6230654</v>
+        <v>6230831</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2024,17 +2024,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 42062-2024 artfynd.xlsx
+++ b/artfynd/A 42062-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120482913</v>
+        <v>120483084</v>
       </c>
       <c r="B2" t="n">
-        <v>80177</v>
+        <v>91801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230185</v>
+        <v>26</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466097</v>
+        <v>465969</v>
       </c>
       <c r="R2" t="n">
-        <v>6230735</v>
+        <v>6230789</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,11 +756,6 @@
           <t>2024-10-17</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt på flera bokar</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,17 +773,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120482728</v>
+        <v>120483051</v>
       </c>
       <c r="B3" t="n">
-        <v>74466</v>
+        <v>94344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,26 +817,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465970</v>
+        <v>466118</v>
       </c>
       <c r="R3" t="n">
-        <v>6230550</v>
+        <v>6230904</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,21 +896,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120482874</v>
+        <v>120482958</v>
       </c>
       <c r="B4" t="n">
         <v>80177</v>
@@ -975,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466131</v>
+        <v>466104</v>
       </c>
       <c r="R4" t="n">
-        <v>6230670</v>
+        <v>6230737</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120483084</v>
+        <v>120483057</v>
       </c>
       <c r="B5" t="n">
-        <v>91801</v>
+        <v>80177</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,21 +1055,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1101,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465969</v>
+        <v>466000</v>
       </c>
       <c r="R5" t="n">
-        <v>6230789</v>
+        <v>6230909</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1156,17 +1137,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1184,7 +1165,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120483057</v>
+        <v>120482913</v>
       </c>
       <c r="B6" t="n">
         <v>80177</v>
@@ -1227,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466000</v>
+        <v>466097</v>
       </c>
       <c r="R6" t="n">
-        <v>6230909</v>
+        <v>6230735</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1263,6 +1244,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på flera bokar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120483051</v>
+        <v>120483065</v>
       </c>
       <c r="B7" t="n">
-        <v>94344</v>
+        <v>80177</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1326,27 +1312,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>230185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1354,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466118</v>
+        <v>465978</v>
       </c>
       <c r="R7" t="n">
-        <v>6230904</v>
+        <v>6230874</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1405,6 +1390,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120482958</v>
+        <v>120482728</v>
       </c>
       <c r="B8" t="n">
-        <v>80177</v>
+        <v>74466</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466104</v>
+        <v>465970</v>
       </c>
       <c r="R8" t="n">
-        <v>6230737</v>
+        <v>6230550</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120482856</v>
+        <v>120483089</v>
       </c>
       <c r="B9" t="n">
-        <v>80177</v>
+        <v>74466</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1587,14 +1587,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Blistorp, Sk</t>
+          <t>N Torparevången, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466127</v>
+        <v>465969</v>
       </c>
       <c r="R9" t="n">
-        <v>6230654</v>
+        <v>6230789</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1646,17 +1646,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120483065</v>
+        <v>120482874</v>
       </c>
       <c r="B10" t="n">
         <v>80177</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465978</v>
+        <v>466131</v>
       </c>
       <c r="R10" t="n">
-        <v>6230874</v>
+        <v>6230670</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120483089</v>
+        <v>120482856</v>
       </c>
       <c r="B11" t="n">
-        <v>74466</v>
+        <v>80177</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1839,14 +1839,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Torparevången, Sk</t>
+          <t>N Blistorp, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465969</v>
+        <v>466127</v>
       </c>
       <c r="R11" t="n">
-        <v>6230789</v>
+        <v>6230654</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 42062-2024 artfynd.xlsx
+++ b/artfynd/A 42062-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120483051</v>
+        <v>120482958</v>
       </c>
       <c r="B3" t="n">
-        <v>94344</v>
+        <v>80177</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,27 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>230185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466118</v>
+        <v>466104</v>
       </c>
       <c r="R3" t="n">
-        <v>6230904</v>
+        <v>6230737</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,6 +895,21 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120482958</v>
+        <v>120483089</v>
       </c>
       <c r="B4" t="n">
-        <v>80177</v>
+        <v>74466</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466104</v>
+        <v>465969</v>
       </c>
       <c r="R4" t="n">
-        <v>6230737</v>
+        <v>6230789</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,17 +1025,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1165,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120482913</v>
+        <v>120482961</v>
       </c>
       <c r="B6" t="n">
         <v>80177</v>
@@ -1208,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466097</v>
+        <v>466096</v>
       </c>
       <c r="R6" t="n">
-        <v>6230735</v>
+        <v>6230831</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1244,11 +1258,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på flera bokar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120483065</v>
+        <v>120482728</v>
       </c>
       <c r="B7" t="n">
-        <v>80177</v>
+        <v>74466</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1321,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1339,10 +1348,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465978</v>
+        <v>465970</v>
       </c>
       <c r="R7" t="n">
-        <v>6230874</v>
+        <v>6230550</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1394,17 +1403,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120482728</v>
+        <v>120483065</v>
       </c>
       <c r="B8" t="n">
-        <v>74466</v>
+        <v>80177</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,21 +1447,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1465,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465970</v>
+        <v>465978</v>
       </c>
       <c r="R8" t="n">
-        <v>6230550</v>
+        <v>6230874</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1520,17 +1529,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1548,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120483089</v>
+        <v>120482913</v>
       </c>
       <c r="B9" t="n">
-        <v>74466</v>
+        <v>80177</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,21 +1573,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1591,10 +1600,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465969</v>
+        <v>466097</v>
       </c>
       <c r="R9" t="n">
-        <v>6230789</v>
+        <v>6230735</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1629,6 +1638,11 @@
           <t>2024-10-17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt på flera bokar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1646,17 +1660,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1674,10 +1688,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482874</v>
+        <v>120483051</v>
       </c>
       <c r="B10" t="n">
-        <v>80177</v>
+        <v>94344</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,26 +1704,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230185</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1717,10 +1732,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466131</v>
+        <v>466118</v>
       </c>
       <c r="R10" t="n">
-        <v>6230670</v>
+        <v>6230904</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1768,21 +1783,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120482856</v>
+        <v>120482874</v>
       </c>
       <c r="B11" t="n">
         <v>80177</v>
@@ -1839,14 +1839,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Blistorp, Sk</t>
+          <t>N Torparevången, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466127</v>
+        <v>466131</v>
       </c>
       <c r="R11" t="n">
-        <v>6230654</v>
+        <v>6230670</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120482961</v>
+        <v>120482856</v>
       </c>
       <c r="B12" t="n">
         <v>80177</v>
@@ -1965,14 +1965,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Torparevången, Sk</t>
+          <t>N Blistorp, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466096</v>
+        <v>466127</v>
       </c>
       <c r="R12" t="n">
-        <v>6230831</v>
+        <v>6230654</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2024,17 +2024,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 42062-2024 artfynd.xlsx
+++ b/artfynd/A 42062-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120482874</v>
+        <v>120483084</v>
       </c>
       <c r="B2" t="n">
-        <v>80228</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230185</v>
+        <v>26</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466131</v>
+        <v>465969</v>
       </c>
       <c r="R2" t="n">
-        <v>6230670</v>
+        <v>6230789</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,17 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120483089</v>
+        <v>120483051</v>
       </c>
       <c r="B3" t="n">
-        <v>74513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +807,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465969</v>
+        <v>466118</v>
       </c>
       <c r="R3" t="n">
-        <v>6230789</v>
+        <v>6230904</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,21 +886,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120483051</v>
+        <v>120482728</v>
       </c>
       <c r="B4" t="n">
-        <v>94458</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,27 +914,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466118</v>
+        <v>465970</v>
       </c>
       <c r="R4" t="n">
-        <v>6230904</v>
+        <v>6230550</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1022,6 +992,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1039,15 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120482856</v>
+        <v>120483089</v>
       </c>
       <c r="B5" t="n">
-        <v>80228</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,14 +1058,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Blistorp, Sk</t>
+          <t>N Torparevången, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466127</v>
+        <v>465969</v>
       </c>
       <c r="R5" t="n">
-        <v>6230654</v>
+        <v>6230789</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1137,17 +1117,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>skogsek</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1165,15 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120483065</v>
+        <v>120482856</v>
       </c>
       <c r="B6" t="n">
-        <v>80228</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,14 +1179,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Torparevången, Sk</t>
+          <t>N Blistorp, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465978</v>
+        <v>466127</v>
       </c>
       <c r="R6" t="n">
-        <v>6230874</v>
+        <v>6230654</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1263,17 +1238,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1291,15 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120482913</v>
+        <v>120482874</v>
       </c>
       <c r="B7" t="n">
-        <v>80228</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466097</v>
+        <v>466131</v>
       </c>
       <c r="R7" t="n">
-        <v>6230735</v>
+        <v>6230670</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,11 +1340,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt på flera bokar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,15 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120482961</v>
+        <v>120482913</v>
       </c>
       <c r="B8" t="n">
-        <v>80228</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466096</v>
+        <v>466097</v>
       </c>
       <c r="R8" t="n">
-        <v>6230831</v>
+        <v>6230735</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1501,6 +1461,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på flera bokar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,12 +1516,7 @@
         <v>120482958</v>
       </c>
       <c r="B9" t="n">
-        <v>80228</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1674,15 +1634,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120483057</v>
+        <v>120482961</v>
       </c>
       <c r="B10" t="n">
-        <v>80228</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466000</v>
+        <v>466096</v>
       </c>
       <c r="R10" t="n">
-        <v>6230909</v>
+        <v>6230831</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1800,15 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120483084</v>
+        <v>120483057</v>
       </c>
       <c r="B11" t="n">
-        <v>91896</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,21 +1766,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>230185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1843,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465969</v>
+        <v>466000</v>
       </c>
       <c r="R11" t="n">
-        <v>6230789</v>
+        <v>6230909</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1898,17 +1848,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1926,15 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120482728</v>
+        <v>120483065</v>
       </c>
       <c r="B12" t="n">
-        <v>74513</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,21 +1887,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1969,10 +1914,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465970</v>
+        <v>465978</v>
       </c>
       <c r="R12" t="n">
-        <v>6230550</v>
+        <v>6230874</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2024,17 +1969,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 42062-2024 artfynd.xlsx
+++ b/artfynd/A 42062-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483051</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482728</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483089</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482856</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482874</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1510,6 +1545,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482913</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1631,6 +1671,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482958</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1752,6 +1797,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482961</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1873,6 +1923,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483057</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1994,8 +2049,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120483065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>